--- a/StructureDefinition-ophthalmic-visual-acuity.xlsx
+++ b/StructureDefinition-ophthalmic-visual-acuity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T20:04:06+00:00</t>
+    <t>2026-08-19T17:13:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ophthalmic-visual-acuity.xlsx
+++ b/StructureDefinition-ophthalmic-visual-acuity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-19T17:13:42+00:00</t>
+    <t>2026-08-19T17:55:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ophthalmic-visual-acuity.xlsx
+++ b/StructureDefinition-ophthalmic-visual-acuity.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-19T17:55:33+00:00</t>
+    <t>2026-08-25T00:41:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ophthalmic-visual-acuity.xlsx
+++ b/StructureDefinition-ophthalmic-visual-acuity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T00:41:24+00:00</t>
+    <t>2026-08-25T02:25:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ophthalmic-visual-acuity.xlsx
+++ b/StructureDefinition-ophthalmic-visual-acuity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T02:25:39+00:00</t>
+    <t>2026-08-25T18:52:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ophthalmic-visual-acuity.xlsx
+++ b/StructureDefinition-ophthalmic-visual-acuity.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T18:52:20+00:00</t>
+    <t>2026-09-01T17:43:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -292,7 +292,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}inv-va-laterality:Visual Acuity should have a bodySite indicating which eye (may be absent for binocular measurements) {bodySite.exists()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -926,9 +926,6 @@
     <t>valueCodeableConcept</t>
   </si>
   <si>
-    <t>extensible</t>
-  </si>
-  <si>
     <t>https://YasniiSS.github.io/fhir4eyes/ValueSet/low-vision-assessment-vs</t>
   </si>
   <si>
@@ -946,6 +943,9 @@
   </si>
   <si>
     <t>For many results it is necessary to handle exceptional values in measurements.</t>
+  </si>
+  <si>
+    <t>extensible</t>
   </si>
   <si>
     <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
@@ -5077,11 +5077,11 @@
         <v>83</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>287</v>
+        <v>183</v>
       </c>
       <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>83</v>
@@ -5134,10 +5134,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5163,16 +5163,16 @@
         <v>192</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="N25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>83</v>
@@ -5197,7 +5197,7 @@
         <v>83</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="Y25" t="s" s="2">
         <v>294</v>
@@ -5221,7 +5221,7 @@
         <v>83</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -5319,7 +5319,7 @@
         <v>83</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="Y26" t="s" s="2">
         <v>304</v>
@@ -9260,7 +9260,7 @@
         <v>497</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>83</v>
@@ -9285,7 +9285,7 @@
         <v>83</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="Y59" t="s" s="2">
         <v>294</v>
@@ -9407,7 +9407,7 @@
         <v>83</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="Y60" t="s" s="2">
         <v>304</v>
@@ -10836,7 +10836,7 @@
         <v>497</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>83</v>
@@ -10861,7 +10861,7 @@
         <v>83</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="Y72" t="s" s="2">
         <v>294</v>
@@ -10983,7 +10983,7 @@
         <v>83</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="Y73" t="s" s="2">
         <v>304</v>
@@ -12412,7 +12412,7 @@
         <v>497</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>83</v>
@@ -12437,7 +12437,7 @@
         <v>83</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="Y85" t="s" s="2">
         <v>294</v>
@@ -12559,7 +12559,7 @@
         <v>83</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="Y86" t="s" s="2">
         <v>304</v>
@@ -13988,7 +13988,7 @@
         <v>497</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>83</v>
@@ -14013,7 +14013,7 @@
         <v>83</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="Y98" t="s" s="2">
         <v>294</v>
@@ -14135,7 +14135,7 @@
         <v>83</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="Y99" t="s" s="2">
         <v>304</v>
@@ -15564,7 +15564,7 @@
         <v>497</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>83</v>
@@ -15589,7 +15589,7 @@
         <v>83</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="Y111" t="s" s="2">
         <v>294</v>
@@ -15711,7 +15711,7 @@
         <v>83</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="Y112" t="s" s="2">
         <v>304</v>
@@ -17140,7 +17140,7 @@
         <v>497</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>83</v>
@@ -17165,7 +17165,7 @@
         <v>83</v>
       </c>
       <c r="X124" t="s" s="2">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="Y124" t="s" s="2">
         <v>294</v>
@@ -17287,7 +17287,7 @@
         <v>83</v>
       </c>
       <c r="X125" t="s" s="2">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="Y125" t="s" s="2">
         <v>304</v>
